--- a/test/fixtures/xlsx/reserved-words/reserved-words.xlsx
+++ b/test/fixtures/xlsx/reserved-words/reserved-words.xlsx
@@ -59,10 +59,10 @@
     <t xml:space="preserve">bool</t>
   </si>
   <si>
-    <t xml:space="preserve">Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">operator: keyword in C++</t>
+    <t xml:space="preserve">*Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">operator: keyword in C++, and a secondary index</t>
   </si>
   <si>
     <t xml:space="preserve">Namespace</t>
